--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/IDAHO_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/IDAHO_2021.xlsx
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C179">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C188">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C518">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C527">
@@ -11857,7 +11857,7 @@
         <v>41</v>
       </c>
       <c r="D639">
-        <v>0.009414466130884041</v>
+        <v>0.00941446613088404</v>
       </c>
     </row>
     <row r="640">
